--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T05:11:07+00:00</t>
+    <t>2026-03-16T07:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T07:24:26+00:00</t>
+    <t>2026-03-16T20:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:48:05+00:00</t>
+    <t>2026-03-16T20:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:59:47+00:00</t>
+    <t>2026-03-16T21:16:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:16:15+00:00</t>
+    <t>2026-03-16T21:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:44:19+00:00</t>
+    <t>2026-03-16T21:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:58:37+00:00</t>
+    <t>2026-03-16T22:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:06:54+00:00</t>
+    <t>2026-03-16T22:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:26:22+00:00</t>
+    <t>2026-03-19T20:53:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T20:53:49+00:00</t>
+    <t>2026-03-19T21:27:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T21:27:42+00:00</t>
+    <t>2026-04-08T04:20:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$69</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2610" uniqueCount="453">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:20:57+00:00</t>
+    <t>2026-04-10T05:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -867,7 +867,7 @@
     <t>Patient.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address|Address}
+    <t xml:space="preserve">Address {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address}
 </t>
   </si>
   <si>
@@ -918,6 +918,89 @@
   </si>
   <si>
     <t>PID-16</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Patient.maritalStatus.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Patient.multipleBirth[x]</t>
@@ -1002,29 +1085,7 @@
     <t>Patient.contact.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Patient.contact.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Patient.contact.modifierExtension</t>
@@ -1065,6 +1126,18 @@
     <t>NK1-7, NK1-3</t>
   </si>
   <si>
+    <t>Patient.contact.relationship.id</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.coding</t>
+  </si>
+  <si>
+    <t>Patient.contact.relationship.text</t>
+  </si>
+  <si>
     <t>Patient.contact.name</t>
   </si>
   <si>
@@ -1219,6 +1292,18 @@
   </si>
   <si>
     <t>PID-15, LAN-2</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.id</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.extension</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.coding</t>
+  </si>
+  <si>
+    <t>Patient.communication.language.text</t>
   </si>
   <si>
     <t>Patient.communication.preferred</t>
@@ -1668,11 +1753,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO57"/>
+  <dimension ref="A1:AO69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="33.83984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.1015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.1015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="18.91015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1699,7 +1784,7 @@
     <col min="26" max="26" width="46.8203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="27.49609375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1709,7 +1794,7 @@
     <col min="37" max="37" width="134.453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="34.98828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="33.76171875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="39.109375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="34.35546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -5130,7 +5215,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>278</v>
       </c>
@@ -5149,7 +5234,7 @@
         <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>81</v>
@@ -5281,12 +5366,8 @@
       <c r="M31" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N31" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5334,7 +5415,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5346,19 +5427,19 @@
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>293</v>
+        <v>220</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
@@ -5366,14 +5447,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5392,20 +5473,18 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>296</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5441,19 +5520,19 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5465,30 +5544,30 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>301</v>
+        <v>220</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5502,28 +5581,28 @@
         <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5584,30 +5663,30 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>309</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5621,25 +5700,29 @@
         <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -5687,7 +5770,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5699,10 +5782,10 @@
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>220</v>
+        <v>312</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
@@ -5711,7 +5794,7 @@
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -5719,21 +5802,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -5745,18 +5828,20 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>134</v>
+        <v>315</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -5804,31 +5889,31 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>81</v>
+        <v>321</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -5836,14 +5921,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>321</v>
+        <v>81</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5856,25 +5941,25 @@
         <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>134</v>
+        <v>323</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>192</v>
+        <v>326</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>193</v>
+        <v>327</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5923,7 +6008,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5935,19 +6020,19 @@
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>132</v>
+        <v>328</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>81</v>
+        <v>329</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -5955,10 +6040,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5981,17 +6066,19 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6016,11 +6103,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6038,7 +6127,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6050,10 +6139,10 @@
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>336</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>220</v>
@@ -6062,7 +6151,7 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6070,10 +6159,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6096,18 +6185,16 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>223</v>
+        <v>288</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>333</v>
+        <v>289</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>334</v>
+        <v>290</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>335</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6155,7 +6242,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>332</v>
+        <v>291</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6167,19 +6254,19 @@
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6187,14 +6274,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6213,20 +6300,18 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>232</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>338</v>
+        <v>293</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>339</v>
+        <v>294</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6274,7 +6359,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>337</v>
+        <v>296</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6286,63 +6371,65 @@
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>341</v>
+        <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I40" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I40" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>270</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N40" s="2"/>
+      <c r="N40" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>345</v>
+        <v>193</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6391,42 +6478,42 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>275</v>
+        <v>132</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6437,10 +6524,10 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>81</v>
@@ -6449,17 +6536,17 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>109</v>
+        <v>279</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6486,11 +6573,9 @@
       <c r="X41" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Y41" t="s" s="2">
-        <v>246</v>
-      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>247</v>
+        <v>349</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
@@ -6508,13 +6593,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -6523,7 +6608,7 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>248</v>
+        <v>350</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>220</v>
@@ -6566,18 +6651,16 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>353</v>
+        <v>288</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>354</v>
+        <v>289</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>355</v>
+        <v>290</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>356</v>
-      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -6625,7 +6708,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>352</v>
+        <v>291</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6634,22 +6717,22 @@
         <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>357</v>
+        <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>358</v>
+        <v>220</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>359</v>
+        <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -6657,21 +6740,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -6683,15 +6766,17 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>361</v>
+        <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>362</v>
+        <v>293</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6728,37 +6813,37 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>360</v>
+        <v>296</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>364</v>
+        <v>220</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
@@ -6770,12 +6855,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6789,28 +6874,28 @@
         <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>299</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>300</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
+        <v>301</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>369</v>
+        <v>302</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6859,7 +6944,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>365</v>
+        <v>303</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6874,27 +6959,27 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>370</v>
+        <v>304</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>371</v>
+        <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6908,25 +6993,29 @@
         <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -6974,7 +7063,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6986,10 +7075,10 @@
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>220</v>
+        <v>312</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>81</v>
@@ -6998,7 +7087,7 @@
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7006,21 +7095,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7032,18 +7121,18 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7091,31 +7180,31 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL46" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>81</v>
+        <v>360</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7123,14 +7212,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>321</v>
+        <v>81</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7143,25 +7232,25 @@
         <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>323</v>
+        <v>363</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>192</v>
+        <v>364</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7210,7 +7299,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>324</v>
+        <v>361</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7222,30 +7311,30 @@
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7253,13 +7342,13 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>81</v>
@@ -7268,19 +7357,17 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7305,13 +7392,13 @@
         <v>81</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>81</v>
@@ -7329,10 +7416,10 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>89</v>
@@ -7344,16 +7431,16 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>380</v>
+        <v>275</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>381</v>
+        <v>220</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -7361,10 +7448,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7387,19 +7474,17 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>213</v>
+        <v>109</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -7424,13 +7509,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7448,7 +7533,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7463,16 +7548,16 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>388</v>
+        <v>248</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>389</v>
+        <v>220</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>81</v>
@@ -7480,21 +7565,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7506,18 +7591,18 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7565,22 +7650,22 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>220</v>
@@ -7589,7 +7674,7 @@
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
@@ -7597,10 +7682,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7620,23 +7705,19 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -7684,7 +7765,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7699,10 +7780,10 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>404</v>
+        <v>220</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
@@ -7716,10 +7797,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7736,25 +7817,25 @@
         <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7803,7 +7884,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7818,10 +7899,10 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>220</v>
+        <v>395</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -7835,10 +7916,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7861,13 +7942,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7918,7 +7999,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7950,10 +8031,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7979,10 +8060,10 @@
         <v>134</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>192</v>
@@ -8035,7 +8116,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8067,14 +8148,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8096,10 +8177,10 @@
         <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>192</v>
@@ -8154,7 +8235,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8184,12 +8265,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8203,27 +8284,29 @@
         <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>415</v>
+        <v>279</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8247,13 +8330,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8271,7 +8354,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>89</v>
@@ -8286,16 +8369,16 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>202</v>
+        <v>404</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>220</v>
+        <v>405</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8303,10 +8386,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8314,7 +8397,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>89</v>
@@ -8326,16 +8409,16 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>421</v>
+        <v>289</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>422</v>
+        <v>290</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8362,13 +8445,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8386,10 +8469,10 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>420</v>
+        <v>291</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>89</v>
@@ -8398,26 +8481,1438 @@
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK57" t="s" s="2">
+      <c r="AK59" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO57" t="s" s="2">
+      <c r="AM62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO57">
+  <autoFilter ref="A1:AO69">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8427,7 +9922,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
+  <conditionalFormatting sqref="A2:AI68">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:32:03+00:00</t>
+    <t>2026-04-10T05:44:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2610" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2647" uniqueCount="458">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:44:36+00:00</t>
+    <t>2026-05-26T03:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,7 +462,7 @@
     <t>nationality</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-nationality|5.2.0}
+    <t xml:space="preserve">Extension {patient-nationality}
 </t>
   </si>
   <si>
@@ -478,7 +478,7 @@
     <t>religion</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-religion|5.2.0}
+    <t xml:space="preserve">Extension {patient-religion}
 </t>
   </si>
   <si>
@@ -494,7 +494,7 @@
     <t>genderIdentity</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {individual-genderIdentity|5.2.0}
+    <t xml:space="preserve">Extension {individual-genderIdentity}
 </t>
   </si>
   <si>
@@ -597,7 +597,7 @@
     <t>sex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {individual-recordedSexOrGender|5.2.0}
+    <t xml:space="preserve">Extension {individual-recordedSexOrGender}
 </t>
   </si>
   <si>
@@ -605,6 +605,22 @@
   </si>
   <si>
     <t>A sex or gender property for the individual from a document or other record</t>
+  </si>
+  <si>
+    <t>Patient.extension:pwdDisability</t>
+  </si>
+  <si>
+    <t>pwdDisability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-pwd-disability}
+</t>
+  </si>
+  <si>
+    <t>PH Core PWD Disability Registration</t>
+  </si>
+  <si>
+    <t>Extension for Person With Disability (PWD) registration information. Captures PWD ID number, type of disability, and ID expiration date as issued by the PDAO (Persons with Disability Affairs Office).</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -1201,7 +1217,7 @@
     <t>Patient.contact.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-organization)
 </t>
   </si>
   <si>
@@ -1337,7 +1353,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-practitioner|http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-practitionerrole|http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-organization)
 </t>
   </si>
   <si>
@@ -1408,7 +1424,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-patient|http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-relatedperson)
 </t>
   </si>
   <si>
@@ -1753,7 +1769,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO69"/>
+  <dimension ref="A1:AO70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.1015625" customWidth="true" bestFit="true"/>
@@ -1766,7 +1782,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.94140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="180.09375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3911,43 +3927,41 @@
         <v>188</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N19" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="O19" t="s" s="2">
-        <v>193</v>
-      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
       </c>
@@ -3995,7 +4009,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4004,13 +4018,13 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>140</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>81</v>
@@ -4027,14 +4041,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4047,23 +4061,25 @@
         <v>81</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4100,19 +4116,19 @@
         <v>81</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4124,34 +4140,32 @@
         <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>202</v>
+        <v>132</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>81</v>
       </c>
@@ -4163,7 +4177,7 @@
         <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>81</v>
@@ -4172,17 +4186,17 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4219,19 +4233,19 @@
         <v>81</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4246,16 +4260,16 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>81</v>
@@ -4263,13 +4277,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>81</v>
@@ -4291,17 +4305,17 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4350,7 +4364,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4365,29 +4379,31 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4396,38 +4412,34 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q23" t="s" s="2">
-        <v>218</v>
-      </c>
+      <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4471,13 +4483,13 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
@@ -4486,27 +4498,27 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4517,36 +4529,38 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I24" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="P24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q24" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L24" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="P24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
         <v>81</v>
       </c>
@@ -4590,13 +4604,13 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>81</v>
@@ -4605,16 +4619,16 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>81</v>
+        <v>226</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>230</v>
+        <v>81</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -4622,10 +4636,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4648,19 +4662,19 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -4709,7 +4723,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4724,16 +4738,16 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -4741,10 +4755,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4755,7 +4769,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>90</v>
@@ -4767,19 +4781,19 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>109</v>
+        <v>237</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -4804,13 +4818,13 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>246</v>
+        <v>81</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>247</v>
+        <v>81</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4828,13 +4842,13 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
@@ -4843,16 +4857,16 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -4860,10 +4874,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4886,19 +4900,19 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>252</v>
+        <v>109</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -4923,13 +4937,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>81</v>
+        <v>251</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -4947,7 +4961,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4962,27 +4976,27 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>260</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4996,28 +5010,28 @@
         <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5066,7 +5080,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5081,27 +5095,27 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>81</v>
+        <v>265</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5112,31 +5126,31 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I29" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5185,13 +5199,13 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
@@ -5200,16 +5214,16 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>276</v>
+        <v>225</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
@@ -5217,10 +5231,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5231,7 +5245,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>90</v>
@@ -5240,20 +5254,22 @@
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
@@ -5278,11 +5294,13 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>283</v>
+        <v>81</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5300,13 +5318,13 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
@@ -5315,27 +5333,27 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5349,7 +5367,7 @@
         <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>81</v>
@@ -5358,16 +5376,18 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5391,13 +5411,11 @@
         <v>81</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>81</v>
@@ -5415,7 +5433,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5427,19 +5445,19 @@
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>81</v>
+        <v>291</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
@@ -5454,14 +5472,14 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
@@ -5473,17 +5491,15 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>134</v>
+        <v>293</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5520,16 +5536,16 @@
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>296</v>
@@ -5538,16 +5554,16 @@
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>81</v>
@@ -5562,7 +5578,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>297</v>
       </c>
@@ -5571,7 +5587,7 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5581,29 +5597,27 @@
         <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M33" t="s" s="2">
-        <v>300</v>
-      </c>
       <c r="N33" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
       </c>
@@ -5639,19 +5653,19 @@
         <v>81</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5663,10 +5677,10 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>304</v>
+        <v>225</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
@@ -5675,7 +5689,7 @@
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -5683,10 +5697,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5697,7 +5711,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>90</v>
@@ -5709,19 +5723,19 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -5770,13 +5784,13 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>81</v>
@@ -5785,7 +5799,7 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
@@ -5794,18 +5808,18 @@
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5819,28 +5833,28 @@
         <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -5889,7 +5903,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5904,16 +5918,16 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -5921,10 +5935,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5935,7 +5949,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -5947,19 +5961,19 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6008,13 +6022,13 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
@@ -6023,16 +6037,16 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6040,10 +6054,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6066,19 +6080,19 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6127,7 +6141,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6139,19 +6153,19 @@
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>336</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>81</v>
+        <v>334</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6159,10 +6173,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6173,7 +6187,7 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6185,16 +6199,20 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>288</v>
+        <v>336</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>289</v>
+        <v>337</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6242,25 +6260,25 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>291</v>
+        <v>335</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>220</v>
+        <v>342</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>81</v>
+        <v>225</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
@@ -6274,21 +6292,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6300,17 +6318,15 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>134</v>
+        <v>293</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6365,16 +6381,16 @@
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>81</v>
@@ -6391,14 +6407,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>341</v>
+        <v>194</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6411,26 +6427,24 @@
         <v>81</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>342</v>
+        <v>298</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6478,7 +6492,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>344</v>
+        <v>301</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6493,7 +6507,7 @@
         <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -6508,7 +6522,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>345</v>
       </c>
@@ -6517,7 +6531,7 @@
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>81</v>
+        <v>346</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6527,26 +6541,28 @@
         <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I41" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I41" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>279</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="O41" t="s" s="2">
-        <v>348</v>
+        <v>198</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6571,29 +6587,31 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6605,30 +6623,30 @@
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" hidden="true">
-      <c r="A42" t="s" s="2">
-        <v>352</v>
-      </c>
       <c r="B42" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6639,10 +6657,10 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>81</v>
@@ -6651,16 +6669,18 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>289</v>
+        <v>351</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>290</v>
+        <v>352</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -6684,13 +6704,11 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -6708,31 +6726,31 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>291</v>
+        <v>350</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>220</v>
+        <v>355</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>81</v>
+        <v>225</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>81</v>
+        <v>356</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -6740,21 +6758,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -6766,17 +6784,15 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>134</v>
+        <v>293</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6813,16 +6829,16 @@
         <v>81</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>296</v>
@@ -6831,16 +6847,16 @@
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>81</v>
@@ -6855,16 +6871,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6874,29 +6890,27 @@
         <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>300</v>
-      </c>
       <c r="N44" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -6932,19 +6946,19 @@
         <v>81</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6956,10 +6970,10 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>304</v>
+        <v>225</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
@@ -6968,7 +6982,7 @@
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
@@ -6976,10 +6990,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6990,7 +7004,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>90</v>
@@ -7002,19 +7016,19 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="O45" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7063,13 +7077,13 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
@@ -7078,7 +7092,7 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>81</v>
@@ -7087,18 +7101,18 @@
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7112,26 +7126,28 @@
         <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>223</v>
+        <v>293</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>357</v>
+        <v>312</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>359</v>
+        <v>315</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7180,7 +7196,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>356</v>
+        <v>316</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7195,16 +7211,16 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>228</v>
+        <v>317</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>360</v>
+        <v>318</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7226,7 +7242,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7238,7 +7254,7 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>362</v>
@@ -7246,11 +7262,9 @@
       <c r="M47" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7305,7 +7319,7 @@
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
@@ -7314,10 +7328,10 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7329,7 +7343,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>366</v>
       </c>
@@ -7345,10 +7359,10 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>81</v>
@@ -7357,7 +7371,7 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>367</v>
@@ -7365,9 +7379,11 @@
       <c r="M48" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="N48" s="2"/>
+      <c r="N48" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>369</v>
+        <v>241</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7422,7 +7438,7 @@
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
@@ -7431,10 +7447,10 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
@@ -7446,7 +7462,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>371</v>
       </c>
@@ -7465,7 +7481,7 @@
         <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>81</v>
@@ -7474,7 +7490,7 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>109</v>
+        <v>275</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>372</v>
@@ -7509,13 +7525,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>246</v>
+        <v>81</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>247</v>
+        <v>81</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7548,10 +7564,10 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
@@ -7591,17 +7607,17 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -7626,13 +7642,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>81</v>
+        <v>251</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7659,22 +7675,22 @@
         <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>382</v>
+        <v>253</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
@@ -7682,10 +7698,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7708,16 +7724,18 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="L51" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -7765,7 +7783,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7774,22 +7792,22 @@
         <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
@@ -7811,7 +7829,7 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -7823,20 +7841,16 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N52" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="O52" t="s" s="2">
-        <v>393</v>
-      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
       </c>
@@ -7890,7 +7904,7 @@
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
@@ -7899,10 +7913,10 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>395</v>
+        <v>225</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -7916,10 +7930,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7930,7 +7944,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -7942,16 +7956,20 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>288</v>
+        <v>336</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>289</v>
+        <v>395</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -7999,25 +8017,25 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>291</v>
+        <v>394</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>220</v>
+        <v>399</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>81</v>
+        <v>400</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -8031,21 +8049,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -8057,17 +8075,15 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>134</v>
+        <v>293</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8122,16 +8138,16 @@
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>81</v>
@@ -8148,14 +8164,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>341</v>
+        <v>194</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8168,26 +8184,24 @@
         <v>81</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>342</v>
+        <v>298</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8235,7 +8249,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>344</v>
+        <v>301</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8250,7 +8264,7 @@
         <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>81</v>
@@ -8265,47 +8279,47 @@
         <v>81</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>81</v>
+        <v>346</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I56" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I56" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>279</v>
+        <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>400</v>
+        <v>347</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>401</v>
+        <v>348</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>402</v>
+        <v>197</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>403</v>
+        <v>198</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8330,13 +8344,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8354,42 +8368,42 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="B57" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8397,13 +8411,13 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>81</v>
@@ -8412,16 +8426,20 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>289</v>
+        <v>405</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
@@ -8445,13 +8463,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8469,10 +8487,10 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>291</v>
+        <v>404</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>89</v>
@@ -8481,19 +8499,19 @@
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>220</v>
+        <v>409</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>81</v>
+        <v>410</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>81</v>
+        <v>411</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8501,21 +8519,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>81</v>
@@ -8527,17 +8545,15 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>134</v>
+        <v>293</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8574,16 +8590,16 @@
         <v>81</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>295</v>
+        <v>81</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>296</v>
@@ -8592,16 +8608,16 @@
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
@@ -8616,16 +8632,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8635,29 +8651,27 @@
         <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>300</v>
-      </c>
       <c r="N59" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -8693,19 +8707,19 @@
         <v>81</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8717,10 +8731,10 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>304</v>
+        <v>225</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
@@ -8729,7 +8743,7 @@
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>305</v>
+        <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -8737,10 +8751,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8751,7 +8765,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>90</v>
@@ -8763,19 +8777,19 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -8824,13 +8838,13 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
@@ -8839,7 +8853,7 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>81</v>
@@ -8848,18 +8862,18 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8873,28 +8887,28 @@
         <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>213</v>
+        <v>293</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>412</v>
+        <v>312</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>413</v>
+        <v>313</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>414</v>
+        <v>314</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>415</v>
+        <v>315</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -8943,7 +8957,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>411</v>
+        <v>316</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8958,16 +8972,16 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>416</v>
+        <v>317</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>417</v>
+        <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>418</v>
+        <v>318</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>
@@ -8975,21 +8989,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>420</v>
+        <v>81</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9001,18 +9015,20 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>421</v>
+        <v>218</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9060,13 +9076,13 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
@@ -9075,16 +9091,16 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>220</v>
+        <v>422</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -9092,21 +9108,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9115,23 +9131,21 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>377</v>
+        <v>426</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="N63" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>431</v>
-      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>81</v>
       </c>
@@ -9179,13 +9193,13 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
@@ -9194,16 +9208,16 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>382</v>
+        <v>430</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>432</v>
+        <v>225</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>81</v>
@@ -9211,10 +9225,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9225,31 +9239,31 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>331</v>
+        <v>382</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9298,13 +9312,13 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
@@ -9313,10 +9327,10 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>220</v>
+        <v>437</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
@@ -9330,10 +9344,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9344,28 +9358,32 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>288</v>
+        <v>336</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>289</v>
+        <v>439</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
       </c>
@@ -9413,25 +9431,25 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>291</v>
+        <v>438</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>220</v>
+        <v>443</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>81</v>
+        <v>225</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
@@ -9445,21 +9463,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
@@ -9471,17 +9489,15 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>134</v>
+        <v>293</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -9536,16 +9552,16 @@
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>81</v>
@@ -9562,14 +9578,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>341</v>
+        <v>194</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9582,26 +9598,24 @@
         <v>81</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>342</v>
+        <v>298</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
@@ -9649,7 +9663,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>344</v>
+        <v>301</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9664,7 +9678,7 @@
         <v>140</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>81</v>
@@ -9681,44 +9695,46 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>81</v>
+        <v>346</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>443</v>
+        <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>444</v>
+        <v>347</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>445</v>
+        <v>348</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
       </c>
@@ -9766,31 +9782,31 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>202</v>
+        <v>132</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
@@ -9798,10 +9814,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9824,7 +9840,7 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>109</v>
+        <v>448</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>449</v>
@@ -9832,7 +9848,9 @@
       <c r="M69" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="N69" s="2"/>
+      <c r="N69" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -9857,13 +9875,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -9881,7 +9899,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>89</v>
@@ -9896,23 +9914,138 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL69" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AO69" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO69">
+  <autoFilter ref="A1:AO70">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9922,7 +10055,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T03:51:01+00:00</t>
+    <t>2026-05-26T04:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-patient.xlsx
+++ b/dev/StructureDefinition-ph-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T04:00:40+00:00</t>
+    <t>2026-05-26T04:36:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
